--- a/artfynd/A 24688-2025 artfynd.xlsx
+++ b/artfynd/A 24688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105874715</v>
+        <v>137109635</v>
       </c>
       <c r="B2" t="n">
-        <v>58497</v>
+        <v>58490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>100058</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,7 +713,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
@@ -757,12 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-07</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-07</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,6 +801,120 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137109635</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>105874715</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Laxvägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>466673</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6216923</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bromölla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ivetofta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-01-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-01-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Hans Berggren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hans Berggren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105874715</t>
         </is>
@@ -795,6 +923,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24688-2025 artfynd.xlsx
+++ b/artfynd/A 24688-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109635</v>
       </c>
       <c r="B2" t="n">
-        <v>58490</v>
+        <v>58503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24688-2025 artfynd.xlsx
+++ b/artfynd/A 24688-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109635</v>
       </c>
       <c r="B2" t="n">
-        <v>58503</v>
+        <v>58505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24688-2025 artfynd.xlsx
+++ b/artfynd/A 24688-2025 artfynd.xlsx
@@ -713,17 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>

--- a/artfynd/A 24688-2025 artfynd.xlsx
+++ b/artfynd/A 24688-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109635</v>
       </c>
       <c r="B2" t="n">
-        <v>58505</v>
+        <v>58515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24688-2025 artfynd.xlsx
+++ b/artfynd/A 24688-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109635</v>
       </c>
       <c r="B2" t="n">
-        <v>58515</v>
+        <v>58517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24688-2025 artfynd.xlsx
+++ b/artfynd/A 24688-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109635</v>
       </c>
       <c r="B2" t="n">
-        <v>58517</v>
+        <v>58519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24688-2025 artfynd.xlsx
+++ b/artfynd/A 24688-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137109635</v>
       </c>
       <c r="B2" t="n">
-        <v>58519</v>
+        <v>58522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
